--- a/scripts/productos-digitales/guia-chocolateria/build/sensibilidad-al-precio-del-cacao.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/sensibilidad-al-precio-del-cacao.xlsx
@@ -243,7 +243,7 @@
   <commentList>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -268,7 +268,7 @@
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="D8" authorId="0" shapeId="0">
@@ -278,17 +278,17 @@
     </comment>
     <comment ref="F8" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="F10" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="I15" authorId="0" shapeId="0">
